--- a/docs/_baseline/habitat_bulk.xlsx
+++ b/docs/_baseline/habitat_bulk.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95">
   <si>
     <t>※ 엑셀 기반 수질/생태계 데이터 베이스 작성/관리 시 주의 사항</t>
   </si>
@@ -316,9 +316,6 @@
   </si>
   <si>
     <t>곡교천</t>
-  </si>
-  <si>
-    <t>평지형</t>
   </si>
   <si>
     <t>맑음</t>
@@ -2843,7 +2840,7 @@
         <v>83</v>
       </c>
       <c r="F8" s="53" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="G8" s="53"/>
       <c r="H8" s="53"/>
@@ -3638,7 +3635,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="55" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G11" s="55"/>
       <c r="H11" s="55"/>
@@ -3903,7 +3900,7 @@
         <v>84</v>
       </c>
       <c r="F12" s="56" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G12" s="56"/>
       <c r="H12" s="56"/>
@@ -4168,7 +4165,7 @@
         <v>85</v>
       </c>
       <c r="F13" s="56" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G13" s="56"/>
       <c r="H13" s="56"/>
@@ -4692,7 +4689,7 @@
       </c>
       <c r="E15" s="47"/>
       <c r="F15" s="57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G15" s="57"/>
       <c r="H15" s="57"/>
